--- a/01_Input/00_CO Validation/Guatemala - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Guatemala - Energy Projects.xlsx
@@ -235,7 +235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -351,9 +351,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -437,6 +434,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -995,15 +1012,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="40" t="n"/>
-      <c r="M3" s="41" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M3" s="34" t="n"/>
       <c r="N3" s="32" t="n"/>
       <c r="O3" s="33" t="n"/>
       <c r="P3" s="9" t="n"/>
@@ -1085,7 +1098,7 @@
       <c r="X6" s="3" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1116,17 +1129,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1144,288 +1152,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
